--- a/beta_12wok/report_cleansing_ps.xlsx
+++ b/beta_12wok/report_cleansing_ps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="408">
   <si>
     <t>C_SERVICENUM</t>
   </si>
@@ -1111,7 +1111,10 @@
     <t>BALI TIMUR</t>
   </si>
   <si>
-    <t>BALI TENGAH</t>
+    <t>BALI TENGAH 2</t>
+  </si>
+  <si>
+    <t>BALI TENGAH 1</t>
   </si>
   <si>
     <t>BALI BARAT</t>
@@ -1120,109 +1123,109 @@
     <t>MANGGARAI</t>
   </si>
   <si>
+    <t>ENDE SIKKA - FLORES TIMUR</t>
+  </si>
+  <si>
+    <t>SUMBAWA BARAT - SUMBAWA TIMUR</t>
+  </si>
+  <si>
+    <t>LOMBOK</t>
+  </si>
+  <si>
+    <t>KUPANG ROTE - MALAKA TIMTIM BELU</t>
+  </si>
+  <si>
+    <t>SUMBA</t>
+  </si>
+  <si>
+    <t>SUMBAWA BARAT</t>
+  </si>
+  <si>
+    <t>LOMBOK 1</t>
+  </si>
+  <si>
+    <t>SUMBAWA TIMUR</t>
+  </si>
+  <si>
+    <t>LOMBOK 2</t>
+  </si>
+  <si>
+    <t>BANGLI</t>
+  </si>
+  <si>
+    <t>KLUNGKUNG</t>
+  </si>
+  <si>
+    <t>BADUNG</t>
+  </si>
+  <si>
+    <t>KOTA DENPASAR</t>
+  </si>
+  <si>
+    <t>GIANYAR</t>
+  </si>
+  <si>
+    <t>BULELENG</t>
+  </si>
+  <si>
+    <t>TABANAN</t>
+  </si>
+  <si>
+    <t>MANGGARAI TIMUR</t>
+  </si>
+  <si>
+    <t>ALOR</t>
+  </si>
+  <si>
+    <t>KOTA MATARAM</t>
+  </si>
+  <si>
+    <t>MANGGARAI BARAT</t>
+  </si>
+  <si>
+    <t>LOMBOK BARAT</t>
+  </si>
+  <si>
+    <t>BELU</t>
+  </si>
+  <si>
+    <t>LOMBOK UTARA</t>
+  </si>
+  <si>
+    <t>BIMA</t>
+  </si>
+  <si>
+    <t>SUMBA TIMUR</t>
+  </si>
+  <si>
+    <t>KOTA BIMA</t>
+  </si>
+  <si>
+    <t>ENDE</t>
+  </si>
+  <si>
+    <t>TIMOR TENGAH SELATAN</t>
+  </si>
+  <si>
+    <t>LOMBOK TENGAH</t>
+  </si>
+  <si>
+    <t>LOMBOK TIMUR</t>
+  </si>
+  <si>
+    <t>TIMOR TENGAH UTARA</t>
+  </si>
+  <si>
+    <t>MALAKA</t>
+  </si>
+  <si>
+    <t>SUMBAWA</t>
+  </si>
+  <si>
+    <t>KOTA KUPANG</t>
+  </si>
+  <si>
     <t>FLORES TIMUR</t>
-  </si>
-  <si>
-    <t>SUMBAWA BARAT</t>
-  </si>
-  <si>
-    <t>LOMBOK</t>
-  </si>
-  <si>
-    <t>MALAKA TIMTIM BELU</t>
-  </si>
-  <si>
-    <t>SUMBAWA TIMUR</t>
-  </si>
-  <si>
-    <t>SUMBA</t>
-  </si>
-  <si>
-    <t>ENDE SIKKA</t>
-  </si>
-  <si>
-    <t>KUPANG ROTE</t>
-  </si>
-  <si>
-    <t>LOMBOK 1</t>
-  </si>
-  <si>
-    <t>LOMBOK 2</t>
-  </si>
-  <si>
-    <t>BANGLI</t>
-  </si>
-  <si>
-    <t>KLUNGKUNG</t>
-  </si>
-  <si>
-    <t>BADUNG</t>
-  </si>
-  <si>
-    <t>KOTA DENPASAR</t>
-  </si>
-  <si>
-    <t>GIANYAR</t>
-  </si>
-  <si>
-    <t>BULELENG</t>
-  </si>
-  <si>
-    <t>TABANAN</t>
-  </si>
-  <si>
-    <t>MANGGARAI TIMUR</t>
-  </si>
-  <si>
-    <t>ALOR</t>
-  </si>
-  <si>
-    <t>KOTA MATARAM</t>
-  </si>
-  <si>
-    <t>MANGGARAI BARAT</t>
-  </si>
-  <si>
-    <t>LOMBOK BARAT</t>
-  </si>
-  <si>
-    <t>BELU</t>
-  </si>
-  <si>
-    <t>LOMBOK UTARA</t>
-  </si>
-  <si>
-    <t>BIMA</t>
-  </si>
-  <si>
-    <t>SUMBA TIMUR</t>
-  </si>
-  <si>
-    <t>KOTA BIMA</t>
-  </si>
-  <si>
-    <t>ENDE</t>
-  </si>
-  <si>
-    <t>TIMOR TENGAH SELATAN</t>
-  </si>
-  <si>
-    <t>LOMBOK TENGAH</t>
-  </si>
-  <si>
-    <t>LOMBOK TIMUR</t>
-  </si>
-  <si>
-    <t>TIMOR TENGAH UTARA</t>
-  </si>
-  <si>
-    <t>MALAKA</t>
-  </si>
-  <si>
-    <t>SUMBAWA</t>
-  </si>
-  <si>
-    <t>KOTA KUPANG</t>
   </si>
   <si>
     <t>SUMBA BARAT</t>
@@ -1653,7 +1656,7 @@
         <v>378</v>
       </c>
       <c r="J2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1682,7 +1685,7 @@
         <v>379</v>
       </c>
       <c r="J3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1711,7 +1714,7 @@
         <v>380</v>
       </c>
       <c r="J4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1740,7 +1743,7 @@
         <v>381</v>
       </c>
       <c r="J5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1763,13 +1766,13 @@
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I6" t="s">
         <v>381</v>
       </c>
       <c r="J6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1798,7 +1801,7 @@
         <v>381</v>
       </c>
       <c r="J7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1827,7 +1830,7 @@
         <v>382</v>
       </c>
       <c r="J8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1850,13 +1853,13 @@
         <v>360</v>
       </c>
       <c r="G9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I9" t="s">
         <v>381</v>
       </c>
       <c r="J9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1885,7 +1888,7 @@
         <v>381</v>
       </c>
       <c r="J10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1914,7 +1917,7 @@
         <v>381</v>
       </c>
       <c r="J11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1937,13 +1940,13 @@
         <v>360</v>
       </c>
       <c r="G12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I12" t="s">
         <v>381</v>
       </c>
       <c r="J12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1966,13 +1969,13 @@
         <v>360</v>
       </c>
       <c r="G13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I13" t="s">
         <v>381</v>
       </c>
       <c r="J13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1995,13 +1998,13 @@
         <v>360</v>
       </c>
       <c r="G14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I14" t="s">
         <v>381</v>
       </c>
       <c r="J14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2024,13 +2027,13 @@
         <v>360</v>
       </c>
       <c r="G15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I15" t="s">
         <v>381</v>
       </c>
       <c r="J15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2053,13 +2056,13 @@
         <v>360</v>
       </c>
       <c r="G16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I16" t="s">
         <v>381</v>
       </c>
       <c r="J16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2082,13 +2085,13 @@
         <v>360</v>
       </c>
       <c r="G17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I17" t="s">
         <v>381</v>
       </c>
       <c r="J17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2117,7 +2120,7 @@
         <v>381</v>
       </c>
       <c r="J18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2140,13 +2143,13 @@
         <v>360</v>
       </c>
       <c r="G19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I19" t="s">
         <v>383</v>
       </c>
       <c r="J19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2169,13 +2172,13 @@
         <v>360</v>
       </c>
       <c r="G20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I20" t="s">
         <v>381</v>
       </c>
       <c r="J20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2198,13 +2201,13 @@
         <v>360</v>
       </c>
       <c r="G21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I21" t="s">
         <v>383</v>
       </c>
       <c r="J21" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2233,7 +2236,7 @@
         <v>380</v>
       </c>
       <c r="J22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2262,7 +2265,7 @@
         <v>380</v>
       </c>
       <c r="J23" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2285,13 +2288,13 @@
         <v>360</v>
       </c>
       <c r="G24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I24" t="s">
         <v>381</v>
       </c>
       <c r="J24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2320,7 +2323,7 @@
         <v>380</v>
       </c>
       <c r="J25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2343,13 +2346,13 @@
         <v>360</v>
       </c>
       <c r="G26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I26" t="s">
         <v>381</v>
       </c>
       <c r="J26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2378,7 +2381,7 @@
         <v>382</v>
       </c>
       <c r="J27" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2407,7 +2410,7 @@
         <v>381</v>
       </c>
       <c r="J28" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2436,7 +2439,7 @@
         <v>381</v>
       </c>
       <c r="J29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2459,13 +2462,13 @@
         <v>360</v>
       </c>
       <c r="G30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I30" t="s">
         <v>384</v>
       </c>
       <c r="J30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2494,7 +2497,7 @@
         <v>380</v>
       </c>
       <c r="J31" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2517,13 +2520,13 @@
         <v>360</v>
       </c>
       <c r="G32" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I32" t="s">
         <v>384</v>
       </c>
       <c r="J32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2546,13 +2549,13 @@
         <v>360</v>
       </c>
       <c r="G33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I33" t="s">
         <v>383</v>
       </c>
       <c r="J33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2575,13 +2578,13 @@
         <v>360</v>
       </c>
       <c r="G34" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I34" t="s">
         <v>381</v>
       </c>
       <c r="J34" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2604,13 +2607,13 @@
         <v>360</v>
       </c>
       <c r="G35" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I35" t="s">
         <v>381</v>
       </c>
       <c r="J35" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2639,7 +2642,7 @@
         <v>380</v>
       </c>
       <c r="J36" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2662,13 +2665,13 @@
         <v>360</v>
       </c>
       <c r="G37" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I37" t="s">
         <v>381</v>
       </c>
       <c r="J37" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2697,7 +2700,7 @@
         <v>382</v>
       </c>
       <c r="J38" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2720,13 +2723,13 @@
         <v>360</v>
       </c>
       <c r="G39" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I39" t="s">
         <v>381</v>
       </c>
       <c r="J39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2755,7 +2758,7 @@
         <v>381</v>
       </c>
       <c r="J40" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2778,13 +2781,13 @@
         <v>360</v>
       </c>
       <c r="G41" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I41" t="s">
         <v>381</v>
       </c>
       <c r="J41" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2813,7 +2816,7 @@
         <v>380</v>
       </c>
       <c r="J42" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2836,13 +2839,13 @@
         <v>360</v>
       </c>
       <c r="G43" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I43" t="s">
         <v>381</v>
       </c>
       <c r="J43" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2865,13 +2868,13 @@
         <v>360</v>
       </c>
       <c r="G44" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I44" t="s">
         <v>383</v>
       </c>
       <c r="J44" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2894,13 +2897,13 @@
         <v>360</v>
       </c>
       <c r="G45" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I45" t="s">
         <v>381</v>
       </c>
       <c r="J45" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2923,13 +2926,13 @@
         <v>360</v>
       </c>
       <c r="G46" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I46" t="s">
         <v>381</v>
       </c>
       <c r="J46" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2952,13 +2955,13 @@
         <v>360</v>
       </c>
       <c r="G47" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I47" t="s">
         <v>384</v>
       </c>
       <c r="J47" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2981,13 +2984,13 @@
         <v>360</v>
       </c>
       <c r="G48" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I48" t="s">
         <v>384</v>
       </c>
       <c r="J48" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3010,13 +3013,13 @@
         <v>360</v>
       </c>
       <c r="G49" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I49" t="s">
         <v>381</v>
       </c>
       <c r="J49" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3045,7 +3048,7 @@
         <v>379</v>
       </c>
       <c r="J50" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3068,13 +3071,13 @@
         <v>360</v>
       </c>
       <c r="G51" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I51" t="s">
         <v>384</v>
       </c>
       <c r="J51" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3103,7 +3106,7 @@
         <v>379</v>
       </c>
       <c r="J52" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3126,13 +3129,13 @@
         <v>360</v>
       </c>
       <c r="G53" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I53" t="s">
         <v>384</v>
       </c>
       <c r="J53" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3155,13 +3158,13 @@
         <v>361</v>
       </c>
       <c r="G54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I54" t="s">
         <v>385</v>
       </c>
       <c r="J54" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3184,13 +3187,13 @@
         <v>361</v>
       </c>
       <c r="G55" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I55" t="s">
         <v>386</v>
       </c>
       <c r="J55" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3213,13 +3216,16 @@
         <v>362</v>
       </c>
       <c r="G56" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H56" t="s">
+        <v>374</v>
       </c>
       <c r="I56" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J56" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3242,16 +3248,16 @@
         <v>362</v>
       </c>
       <c r="G57" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H57" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I57" t="s">
         <v>387</v>
       </c>
       <c r="J57" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3274,13 +3280,13 @@
         <v>361</v>
       </c>
       <c r="G58" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I58" t="s">
         <v>388</v>
       </c>
       <c r="J58" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3303,16 +3309,16 @@
         <v>362</v>
       </c>
       <c r="G59" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H59" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I59" t="s">
         <v>389</v>
       </c>
       <c r="J59" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3335,13 +3341,13 @@
         <v>363</v>
       </c>
       <c r="G60" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I60" t="s">
         <v>390</v>
       </c>
       <c r="J60" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3364,16 +3370,16 @@
         <v>362</v>
       </c>
       <c r="G61" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H61" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I61" t="s">
         <v>387</v>
       </c>
       <c r="J61" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3396,16 +3402,16 @@
         <v>362</v>
       </c>
       <c r="G62" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H62" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I62" t="s">
         <v>391</v>
       </c>
       <c r="J62" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3428,13 +3434,16 @@
         <v>362</v>
       </c>
       <c r="G63" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H63" t="s">
+        <v>376</v>
       </c>
       <c r="I63" t="s">
         <v>392</v>
       </c>
       <c r="J63" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3457,13 +3466,13 @@
         <v>361</v>
       </c>
       <c r="G64" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I64" t="s">
         <v>388</v>
       </c>
       <c r="J64" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3492,7 +3501,7 @@
         <v>393</v>
       </c>
       <c r="J65" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3515,13 +3524,16 @@
         <v>362</v>
       </c>
       <c r="G66" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H66" t="s">
+        <v>376</v>
       </c>
       <c r="I66" t="s">
         <v>394</v>
       </c>
       <c r="J66" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3544,13 +3556,13 @@
         <v>361</v>
       </c>
       <c r="G67" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I67" t="s">
         <v>395</v>
       </c>
       <c r="J67" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3573,13 +3585,13 @@
         <v>363</v>
       </c>
       <c r="G68" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I68" t="s">
         <v>396</v>
       </c>
       <c r="J68" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3602,7 +3614,7 @@
         <v>362</v>
       </c>
       <c r="G69" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H69" t="s">
         <v>377</v>
@@ -3611,7 +3623,7 @@
         <v>397</v>
       </c>
       <c r="J69" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3634,7 +3646,7 @@
         <v>362</v>
       </c>
       <c r="G70" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H70" t="s">
         <v>377</v>
@@ -3643,7 +3655,7 @@
         <v>398</v>
       </c>
       <c r="J70" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3666,13 +3678,16 @@
         <v>362</v>
       </c>
       <c r="G71" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H71" t="s">
+        <v>374</v>
       </c>
       <c r="I71" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J71" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3695,13 +3710,16 @@
         <v>362</v>
       </c>
       <c r="G72" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H72" t="s">
+        <v>376</v>
       </c>
       <c r="I72" t="s">
         <v>392</v>
       </c>
       <c r="J72" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3724,13 +3742,13 @@
         <v>363</v>
       </c>
       <c r="G73" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I73" t="s">
         <v>363</v>
       </c>
       <c r="J73" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3753,13 +3771,13 @@
         <v>363</v>
       </c>
       <c r="G74" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I74" t="s">
         <v>390</v>
       </c>
       <c r="J74" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3782,13 +3800,13 @@
         <v>363</v>
       </c>
       <c r="G75" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I75" t="s">
         <v>399</v>
       </c>
       <c r="J75" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3811,16 +3829,16 @@
         <v>362</v>
       </c>
       <c r="G76" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H76" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I76" t="s">
         <v>387</v>
       </c>
       <c r="J76" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3843,13 +3861,13 @@
         <v>363</v>
       </c>
       <c r="G77" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I77" t="s">
         <v>400</v>
       </c>
       <c r="J77" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3872,13 +3890,13 @@
         <v>363</v>
       </c>
       <c r="G78" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I78" t="s">
         <v>399</v>
       </c>
       <c r="J78" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3901,16 +3919,16 @@
         <v>362</v>
       </c>
       <c r="G79" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H79" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I79" t="s">
         <v>387</v>
       </c>
       <c r="J79" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3933,16 +3951,16 @@
         <v>362</v>
       </c>
       <c r="G80" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H80" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I80" t="s">
         <v>391</v>
       </c>
       <c r="J80" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3965,13 +3983,16 @@
         <v>362</v>
       </c>
       <c r="G81" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H81" t="s">
+        <v>376</v>
       </c>
       <c r="I81" t="s">
         <v>392</v>
       </c>
       <c r="J81" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3994,13 +4015,13 @@
         <v>361</v>
       </c>
       <c r="G82" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I82" t="s">
         <v>395</v>
       </c>
       <c r="J82" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -4023,13 +4044,16 @@
         <v>362</v>
       </c>
       <c r="G83" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H83" t="s">
+        <v>374</v>
       </c>
       <c r="I83" t="s">
         <v>401</v>
       </c>
       <c r="J83" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -4052,13 +4076,16 @@
         <v>362</v>
       </c>
       <c r="G84" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H84" t="s">
+        <v>376</v>
       </c>
       <c r="I84" t="s">
         <v>394</v>
       </c>
       <c r="J84" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -4081,16 +4108,16 @@
         <v>362</v>
       </c>
       <c r="G85" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H85" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I85" t="s">
         <v>387</v>
       </c>
       <c r="J85" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -4113,13 +4140,16 @@
         <v>362</v>
       </c>
       <c r="G86" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H86" t="s">
+        <v>376</v>
       </c>
       <c r="I86" t="s">
         <v>392</v>
       </c>
       <c r="J86" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -4142,13 +4172,13 @@
         <v>363</v>
       </c>
       <c r="G87" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I87" t="s">
         <v>402</v>
       </c>
       <c r="J87" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -4171,16 +4201,16 @@
         <v>362</v>
       </c>
       <c r="G88" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I88" t="s">
         <v>387</v>
       </c>
       <c r="J88" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -4203,7 +4233,7 @@
         <v>362</v>
       </c>
       <c r="G89" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H89" t="s">
         <v>377</v>
@@ -4212,7 +4242,7 @@
         <v>397</v>
       </c>
       <c r="J89" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -4235,16 +4265,16 @@
         <v>362</v>
       </c>
       <c r="G90" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H90" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I90" t="s">
         <v>387</v>
       </c>
       <c r="J90" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -4267,16 +4297,16 @@
         <v>362</v>
       </c>
       <c r="G91" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H91" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I91" t="s">
         <v>387</v>
       </c>
       <c r="J91" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4299,13 +4329,16 @@
         <v>362</v>
       </c>
       <c r="G92" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H92" t="s">
+        <v>376</v>
       </c>
       <c r="I92" t="s">
         <v>394</v>
       </c>
       <c r="J92" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4328,16 +4361,16 @@
         <v>362</v>
       </c>
       <c r="G93" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H93" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I93" t="s">
         <v>387</v>
       </c>
       <c r="J93" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -4360,16 +4393,16 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H94" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I94" t="s">
         <v>389</v>
       </c>
       <c r="J94" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4392,13 +4425,13 @@
         <v>361</v>
       </c>
       <c r="G95" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I95" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="J95" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -4421,13 +4454,13 @@
         <v>361</v>
       </c>
       <c r="G96" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I96" t="s">
         <v>386</v>
       </c>
       <c r="J96" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -4450,13 +4483,13 @@
         <v>363</v>
       </c>
       <c r="G97" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I97" t="s">
         <v>402</v>
       </c>
       <c r="J97" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4479,13 +4512,13 @@
         <v>363</v>
       </c>
       <c r="G98" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I98" t="s">
         <v>402</v>
       </c>
       <c r="J98" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4508,16 +4541,16 @@
         <v>362</v>
       </c>
       <c r="G99" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H99" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I99" t="s">
         <v>387</v>
       </c>
       <c r="J99" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4540,16 +4573,16 @@
         <v>362</v>
       </c>
       <c r="G100" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H100" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I100" t="s">
         <v>387</v>
       </c>
       <c r="J100" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -4575,10 +4608,10 @@
         <v>373</v>
       </c>
       <c r="I101" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J101" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -4601,16 +4634,16 @@
         <v>362</v>
       </c>
       <c r="G102" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H102" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I102" t="s">
         <v>387</v>
       </c>
       <c r="J102" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -4633,7 +4666,7 @@
         <v>362</v>
       </c>
       <c r="G103" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H103" t="s">
         <v>377</v>
@@ -4642,7 +4675,7 @@
         <v>397</v>
       </c>
       <c r="J103" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4665,13 +4698,13 @@
         <v>361</v>
       </c>
       <c r="G104" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I104" t="s">
         <v>386</v>
       </c>
       <c r="J104" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -4694,13 +4727,16 @@
         <v>362</v>
       </c>
       <c r="G105" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H105" t="s">
+        <v>374</v>
       </c>
       <c r="I105" t="s">
         <v>401</v>
       </c>
       <c r="J105" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4723,13 +4759,13 @@
         <v>363</v>
       </c>
       <c r="G106" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I106" t="s">
         <v>402</v>
       </c>
       <c r="J106" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -4752,13 +4788,13 @@
         <v>363</v>
       </c>
       <c r="G107" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I107" t="s">
         <v>363</v>
       </c>
       <c r="J107" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -4781,16 +4817,16 @@
         <v>362</v>
       </c>
       <c r="G108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H108" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I108" t="s">
         <v>387</v>
       </c>
       <c r="J108" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -4813,13 +4849,13 @@
         <v>361</v>
       </c>
       <c r="G109" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I109" t="s">
         <v>395</v>
       </c>
       <c r="J109" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -4842,13 +4878,16 @@
         <v>362</v>
       </c>
       <c r="G110" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="H110" t="s">
+        <v>376</v>
       </c>
       <c r="I110" t="s">
         <v>392</v>
       </c>
       <c r="J110" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -4871,16 +4910,16 @@
         <v>362</v>
       </c>
       <c r="G111" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H111" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I111" t="s">
         <v>387</v>
       </c>
       <c r="J111" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -4903,13 +4942,13 @@
         <v>361</v>
       </c>
       <c r="G112" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I112" t="s">
         <v>386</v>
       </c>
       <c r="J112" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4932,13 +4971,13 @@
         <v>361</v>
       </c>
       <c r="G113" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I113" t="s">
         <v>395</v>
       </c>
       <c r="J113" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4961,13 +5000,13 @@
         <v>361</v>
       </c>
       <c r="G114" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I114" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J114" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -4990,13 +5029,13 @@
         <v>361</v>
       </c>
       <c r="G115" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I115" t="s">
         <v>395</v>
       </c>
       <c r="J115" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -5019,16 +5058,16 @@
         <v>362</v>
       </c>
       <c r="G116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H116" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I116" t="s">
         <v>389</v>
       </c>
       <c r="J116" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -5051,13 +5090,13 @@
         <v>361</v>
       </c>
       <c r="G117" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I117" t="s">
         <v>395</v>
       </c>
       <c r="J117" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -5086,7 +5125,7 @@
         <v>393</v>
       </c>
       <c r="J118" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -5112,10 +5151,10 @@
         <v>373</v>
       </c>
       <c r="I119" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J119" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -5138,13 +5177,13 @@
         <v>363</v>
       </c>
       <c r="G120" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I120" t="s">
         <v>363</v>
       </c>
       <c r="J120" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -5167,7 +5206,7 @@
         <v>362</v>
       </c>
       <c r="G121" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H121" t="s">
         <v>377</v>
@@ -5176,7 +5215,7 @@
         <v>398</v>
       </c>
       <c r="J121" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/beta_12wok/report_cleansing_ps.xlsx
+++ b/beta_12wok/report_cleansing_ps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="405">
   <si>
     <t>C_SERVICENUM</t>
   </si>
@@ -1111,10 +1111,7 @@
     <t>BALI TIMUR</t>
   </si>
   <si>
-    <t>BALI TENGAH 2</t>
-  </si>
-  <si>
-    <t>BALI TENGAH 1</t>
+    <t>BALI TENGAH</t>
   </si>
   <si>
     <t>BALI BARAT</t>
@@ -1123,31 +1120,28 @@
     <t>MANGGARAI</t>
   </si>
   <si>
-    <t>ENDE SIKKA - FLORES TIMUR</t>
-  </si>
-  <si>
-    <t>SUMBAWA BARAT - SUMBAWA TIMUR</t>
+    <t>FLORES TIMUR</t>
+  </si>
+  <si>
+    <t>SUMBAWA BARAT</t>
   </si>
   <si>
     <t>LOMBOK</t>
   </si>
   <si>
-    <t>KUPANG ROTE - MALAKA TIMTIM BELU</t>
+    <t>MALAKA TIMTIM BELU</t>
+  </si>
+  <si>
+    <t>SUMBAWA TIMUR</t>
   </si>
   <si>
     <t>SUMBA</t>
   </si>
   <si>
-    <t>SUMBAWA BARAT</t>
-  </si>
-  <si>
-    <t>LOMBOK 1</t>
-  </si>
-  <si>
-    <t>SUMBAWA TIMUR</t>
-  </si>
-  <si>
-    <t>LOMBOK 2</t>
+    <t>ENDE SIKKA</t>
+  </si>
+  <si>
+    <t>KUPANG ROTE</t>
   </si>
   <si>
     <t>BANGLI</t>
@@ -1223,9 +1217,6 @@
   </si>
   <si>
     <t>KOTA KUPANG</t>
-  </si>
-  <si>
-    <t>FLORES TIMUR</t>
   </si>
   <si>
     <t>SUMBA BARAT</t>
@@ -1653,10 +1644,10 @@
         <v>364</v>
       </c>
       <c r="I2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1682,10 +1673,10 @@
         <v>364</v>
       </c>
       <c r="I3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1711,10 +1702,10 @@
         <v>365</v>
       </c>
       <c r="I4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1740,10 +1731,10 @@
         <v>365</v>
       </c>
       <c r="I5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1766,13 +1757,13 @@
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1798,10 +1789,10 @@
         <v>365</v>
       </c>
       <c r="I7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J7" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1827,10 +1818,10 @@
         <v>364</v>
       </c>
       <c r="I8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1853,13 +1844,13 @@
         <v>360</v>
       </c>
       <c r="G9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1885,10 +1876,10 @@
         <v>365</v>
       </c>
       <c r="I10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J10" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1914,10 +1905,10 @@
         <v>365</v>
       </c>
       <c r="I11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J11" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1940,13 +1931,13 @@
         <v>360</v>
       </c>
       <c r="G12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J12" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1969,13 +1960,13 @@
         <v>360</v>
       </c>
       <c r="G13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J13" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1998,13 +1989,13 @@
         <v>360</v>
       </c>
       <c r="G14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I14" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J14" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2027,13 +2018,13 @@
         <v>360</v>
       </c>
       <c r="G15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I15" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2056,13 +2047,13 @@
         <v>360</v>
       </c>
       <c r="G16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I16" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J16" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2085,13 +2076,13 @@
         <v>360</v>
       </c>
       <c r="G17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J17" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2117,10 +2108,10 @@
         <v>365</v>
       </c>
       <c r="I18" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J18" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2143,13 +2134,13 @@
         <v>360</v>
       </c>
       <c r="G19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J19" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2172,13 +2163,13 @@
         <v>360</v>
       </c>
       <c r="G20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I20" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J20" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2201,13 +2192,13 @@
         <v>360</v>
       </c>
       <c r="G21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J21" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2233,10 +2224,10 @@
         <v>365</v>
       </c>
       <c r="I22" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2262,10 +2253,10 @@
         <v>365</v>
       </c>
       <c r="I23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J23" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2288,13 +2279,13 @@
         <v>360</v>
       </c>
       <c r="G24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I24" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J24" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2320,10 +2311,10 @@
         <v>365</v>
       </c>
       <c r="I25" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J25" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2346,13 +2337,13 @@
         <v>360</v>
       </c>
       <c r="G26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I26" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J26" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2378,10 +2369,10 @@
         <v>364</v>
       </c>
       <c r="I27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J27" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2407,10 +2398,10 @@
         <v>365</v>
       </c>
       <c r="I28" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J28" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2436,10 +2427,10 @@
         <v>365</v>
       </c>
       <c r="I29" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J29" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2462,13 +2453,13 @@
         <v>360</v>
       </c>
       <c r="G30" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I30" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J30" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2494,10 +2485,10 @@
         <v>365</v>
       </c>
       <c r="I31" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J31" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2520,13 +2511,13 @@
         <v>360</v>
       </c>
       <c r="G32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I32" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J32" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2549,13 +2540,13 @@
         <v>360</v>
       </c>
       <c r="G33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I33" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J33" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2578,13 +2569,13 @@
         <v>360</v>
       </c>
       <c r="G34" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I34" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J34" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2607,13 +2598,13 @@
         <v>360</v>
       </c>
       <c r="G35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I35" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J35" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2639,10 +2630,10 @@
         <v>365</v>
       </c>
       <c r="I36" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J36" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2665,13 +2656,13 @@
         <v>360</v>
       </c>
       <c r="G37" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I37" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J37" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2697,10 +2688,10 @@
         <v>364</v>
       </c>
       <c r="I38" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J38" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2723,13 +2714,13 @@
         <v>360</v>
       </c>
       <c r="G39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I39" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J39" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2755,10 +2746,10 @@
         <v>365</v>
       </c>
       <c r="I40" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J40" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2781,13 +2772,13 @@
         <v>360</v>
       </c>
       <c r="G41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I41" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J41" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2813,10 +2804,10 @@
         <v>365</v>
       </c>
       <c r="I42" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J42" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2839,13 +2830,13 @@
         <v>360</v>
       </c>
       <c r="G43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I43" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J43" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2868,13 +2859,13 @@
         <v>360</v>
       </c>
       <c r="G44" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I44" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J44" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2897,13 +2888,13 @@
         <v>360</v>
       </c>
       <c r="G45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I45" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J45" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2926,13 +2917,13 @@
         <v>360</v>
       </c>
       <c r="G46" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I46" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J46" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2955,13 +2946,13 @@
         <v>360</v>
       </c>
       <c r="G47" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I47" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J47" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2984,13 +2975,13 @@
         <v>360</v>
       </c>
       <c r="G48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I48" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J48" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3013,13 +3004,13 @@
         <v>360</v>
       </c>
       <c r="G49" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I49" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J49" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3045,10 +3036,10 @@
         <v>364</v>
       </c>
       <c r="I50" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J50" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3071,13 +3062,13 @@
         <v>360</v>
       </c>
       <c r="G51" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I51" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J51" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3103,10 +3094,10 @@
         <v>364</v>
       </c>
       <c r="I52" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J52" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3129,13 +3120,13 @@
         <v>360</v>
       </c>
       <c r="G53" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J53" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3158,13 +3149,13 @@
         <v>361</v>
       </c>
       <c r="G54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J54" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3187,13 +3178,13 @@
         <v>361</v>
       </c>
       <c r="G55" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I55" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J55" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3216,16 +3207,13 @@
         <v>362</v>
       </c>
       <c r="G56" t="s">
-        <v>370</v>
-      </c>
-      <c r="H56" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I56" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J56" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3248,16 +3236,13 @@
         <v>362</v>
       </c>
       <c r="G57" t="s">
-        <v>371</v>
-      </c>
-      <c r="H57" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I57" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J57" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3280,13 +3265,13 @@
         <v>361</v>
       </c>
       <c r="G58" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J58" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3309,16 +3294,13 @@
         <v>362</v>
       </c>
       <c r="G59" t="s">
-        <v>371</v>
-      </c>
-      <c r="H59" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I59" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J59" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3341,13 +3323,13 @@
         <v>363</v>
       </c>
       <c r="G60" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I60" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J60" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3370,16 +3352,13 @@
         <v>362</v>
       </c>
       <c r="G61" t="s">
-        <v>371</v>
-      </c>
-      <c r="H61" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I61" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J61" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3402,16 +3381,13 @@
         <v>362</v>
       </c>
       <c r="G62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I62" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J62" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3434,16 +3410,13 @@
         <v>362</v>
       </c>
       <c r="G63" t="s">
-        <v>370</v>
-      </c>
-      <c r="H63" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I63" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J63" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3466,13 +3439,13 @@
         <v>361</v>
       </c>
       <c r="G64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I64" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J64" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3498,10 +3471,10 @@
         <v>373</v>
       </c>
       <c r="I65" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J65" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3524,16 +3497,13 @@
         <v>362</v>
       </c>
       <c r="G66" t="s">
-        <v>370</v>
-      </c>
-      <c r="H66" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I66" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J66" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3556,13 +3526,13 @@
         <v>361</v>
       </c>
       <c r="G67" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I67" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J67" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3585,13 +3555,13 @@
         <v>363</v>
       </c>
       <c r="G68" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I68" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J68" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3614,16 +3584,13 @@
         <v>362</v>
       </c>
       <c r="G69" t="s">
-        <v>371</v>
-      </c>
-      <c r="H69" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I69" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J69" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3646,16 +3613,13 @@
         <v>362</v>
       </c>
       <c r="G70" t="s">
-        <v>371</v>
-      </c>
-      <c r="H70" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I70" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J70" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3678,16 +3642,13 @@
         <v>362</v>
       </c>
       <c r="G71" t="s">
-        <v>370</v>
-      </c>
-      <c r="H71" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I71" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J71" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3710,16 +3671,13 @@
         <v>362</v>
       </c>
       <c r="G72" t="s">
-        <v>370</v>
-      </c>
-      <c r="H72" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I72" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J72" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3742,13 +3700,13 @@
         <v>363</v>
       </c>
       <c r="G73" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I73" t="s">
         <v>363</v>
       </c>
       <c r="J73" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3771,13 +3729,13 @@
         <v>363</v>
       </c>
       <c r="G74" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I74" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J74" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3800,13 +3758,13 @@
         <v>363</v>
       </c>
       <c r="G75" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I75" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J75" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3829,16 +3787,13 @@
         <v>362</v>
       </c>
       <c r="G76" t="s">
-        <v>371</v>
-      </c>
-      <c r="H76" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I76" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J76" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3861,13 +3816,13 @@
         <v>363</v>
       </c>
       <c r="G77" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I77" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3890,13 +3845,13 @@
         <v>363</v>
       </c>
       <c r="G78" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I78" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J78" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3919,16 +3874,13 @@
         <v>362</v>
       </c>
       <c r="G79" t="s">
-        <v>371</v>
-      </c>
-      <c r="H79" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I79" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J79" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3951,16 +3903,13 @@
         <v>362</v>
       </c>
       <c r="G80" t="s">
-        <v>371</v>
-      </c>
-      <c r="H80" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I80" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J80" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3983,16 +3932,13 @@
         <v>362</v>
       </c>
       <c r="G81" t="s">
-        <v>370</v>
-      </c>
-      <c r="H81" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I81" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J81" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -4015,13 +3961,13 @@
         <v>361</v>
       </c>
       <c r="G82" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I82" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J82" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -4044,16 +3990,13 @@
         <v>362</v>
       </c>
       <c r="G83" t="s">
-        <v>370</v>
-      </c>
-      <c r="H83" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I83" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J83" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -4076,16 +4019,13 @@
         <v>362</v>
       </c>
       <c r="G84" t="s">
-        <v>370</v>
-      </c>
-      <c r="H84" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I84" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J84" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -4108,16 +4048,13 @@
         <v>362</v>
       </c>
       <c r="G85" t="s">
-        <v>371</v>
-      </c>
-      <c r="H85" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I85" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J85" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -4140,16 +4077,13 @@
         <v>362</v>
       </c>
       <c r="G86" t="s">
-        <v>370</v>
-      </c>
-      <c r="H86" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I86" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J86" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -4172,13 +4106,13 @@
         <v>363</v>
       </c>
       <c r="G87" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I87" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J87" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -4201,16 +4135,13 @@
         <v>362</v>
       </c>
       <c r="G88" t="s">
-        <v>371</v>
-      </c>
-      <c r="H88" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I88" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J88" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -4233,16 +4164,13 @@
         <v>362</v>
       </c>
       <c r="G89" t="s">
-        <v>371</v>
-      </c>
-      <c r="H89" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I89" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J89" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -4265,16 +4193,13 @@
         <v>362</v>
       </c>
       <c r="G90" t="s">
-        <v>371</v>
-      </c>
-      <c r="H90" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I90" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J90" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -4297,16 +4222,13 @@
         <v>362</v>
       </c>
       <c r="G91" t="s">
-        <v>371</v>
-      </c>
-      <c r="H91" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I91" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J91" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4329,16 +4251,13 @@
         <v>362</v>
       </c>
       <c r="G92" t="s">
-        <v>370</v>
-      </c>
-      <c r="H92" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I92" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J92" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4361,16 +4280,13 @@
         <v>362</v>
       </c>
       <c r="G93" t="s">
-        <v>371</v>
-      </c>
-      <c r="H93" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I93" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J93" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -4393,16 +4309,13 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>371</v>
-      </c>
-      <c r="H94" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I94" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J94" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4425,13 +4338,13 @@
         <v>361</v>
       </c>
       <c r="G95" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I95" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="J95" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -4454,13 +4367,13 @@
         <v>361</v>
       </c>
       <c r="G96" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I96" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J96" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -4483,13 +4396,13 @@
         <v>363</v>
       </c>
       <c r="G97" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I97" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J97" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4512,13 +4425,13 @@
         <v>363</v>
       </c>
       <c r="G98" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I98" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J98" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4541,16 +4454,13 @@
         <v>362</v>
       </c>
       <c r="G99" t="s">
-        <v>371</v>
-      </c>
-      <c r="H99" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I99" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J99" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4573,16 +4483,13 @@
         <v>362</v>
       </c>
       <c r="G100" t="s">
-        <v>371</v>
-      </c>
-      <c r="H100" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I100" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J100" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -4608,10 +4515,10 @@
         <v>373</v>
       </c>
       <c r="I101" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J101" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -4634,16 +4541,13 @@
         <v>362</v>
       </c>
       <c r="G102" t="s">
-        <v>371</v>
-      </c>
-      <c r="H102" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I102" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J102" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -4666,16 +4570,13 @@
         <v>362</v>
       </c>
       <c r="G103" t="s">
-        <v>371</v>
-      </c>
-      <c r="H103" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I103" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J103" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4698,13 +4599,13 @@
         <v>361</v>
       </c>
       <c r="G104" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I104" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J104" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -4727,16 +4628,13 @@
         <v>362</v>
       </c>
       <c r="G105" t="s">
-        <v>370</v>
-      </c>
-      <c r="H105" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I105" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J105" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4759,13 +4657,13 @@
         <v>363</v>
       </c>
       <c r="G106" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I106" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J106" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -4788,13 +4686,13 @@
         <v>363</v>
       </c>
       <c r="G107" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I107" t="s">
         <v>363</v>
       </c>
       <c r="J107" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -4817,16 +4715,13 @@
         <v>362</v>
       </c>
       <c r="G108" t="s">
-        <v>371</v>
-      </c>
-      <c r="H108" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I108" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J108" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -4849,13 +4744,13 @@
         <v>361</v>
       </c>
       <c r="G109" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I109" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J109" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -4878,16 +4773,13 @@
         <v>362</v>
       </c>
       <c r="G110" t="s">
-        <v>370</v>
-      </c>
-      <c r="H110" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I110" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J110" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -4910,16 +4802,13 @@
         <v>362</v>
       </c>
       <c r="G111" t="s">
-        <v>371</v>
-      </c>
-      <c r="H111" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I111" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J111" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -4942,13 +4831,13 @@
         <v>361</v>
       </c>
       <c r="G112" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I112" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J112" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4971,13 +4860,13 @@
         <v>361</v>
       </c>
       <c r="G113" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I113" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J113" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -5000,13 +4889,13 @@
         <v>361</v>
       </c>
       <c r="G114" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I114" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J114" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -5029,13 +4918,13 @@
         <v>361</v>
       </c>
       <c r="G115" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I115" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J115" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -5058,16 +4947,13 @@
         <v>362</v>
       </c>
       <c r="G116" t="s">
-        <v>371</v>
-      </c>
-      <c r="H116" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I116" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J116" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -5090,13 +4976,13 @@
         <v>361</v>
       </c>
       <c r="G117" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I117" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J117" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -5122,10 +5008,10 @@
         <v>373</v>
       </c>
       <c r="I118" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J118" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -5151,10 +5037,10 @@
         <v>373</v>
       </c>
       <c r="I119" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J119" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -5177,13 +5063,13 @@
         <v>363</v>
       </c>
       <c r="G120" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I120" t="s">
         <v>363</v>
       </c>
       <c r="J120" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -5206,16 +5092,13 @@
         <v>362</v>
       </c>
       <c r="G121" t="s">
-        <v>371</v>
-      </c>
-      <c r="H121" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I121" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J121" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/beta_12wok/report_cleansing_ps.xlsx
+++ b/beta_12wok/report_cleansing_ps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="404">
   <si>
     <t>C_SERVICENUM</t>
   </si>
@@ -1226,9 +1226,6 @@
   </si>
   <si>
     <t>PS ONLY</t>
-  </si>
-  <si>
-    <t>WITH PS &amp; DJP</t>
   </si>
 </sst>
 </file>
@@ -1879,7 +1876,7 @@
         <v>379</v>
       </c>
       <c r="J10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1995,7 +1992,7 @@
         <v>379</v>
       </c>
       <c r="J14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2111,7 +2108,7 @@
         <v>379</v>
       </c>
       <c r="J18" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2140,7 +2137,7 @@
         <v>381</v>
       </c>
       <c r="J19" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2749,7 +2746,7 @@
         <v>379</v>
       </c>
       <c r="J40" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2778,7 +2775,7 @@
         <v>379</v>
       </c>
       <c r="J41" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -3126,7 +3123,7 @@
         <v>382</v>
       </c>
       <c r="J53" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3184,7 +3181,7 @@
         <v>384</v>
       </c>
       <c r="J55" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3213,7 +3210,7 @@
         <v>369</v>
       </c>
       <c r="J56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3300,7 +3297,7 @@
         <v>387</v>
       </c>
       <c r="J59" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3619,7 +3616,7 @@
         <v>396</v>
       </c>
       <c r="J70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3648,7 +3645,7 @@
         <v>369</v>
       </c>
       <c r="J71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3677,7 +3674,7 @@
         <v>390</v>
       </c>
       <c r="J72" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3938,7 +3935,7 @@
         <v>390</v>
       </c>
       <c r="J81" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3967,7 +3964,7 @@
         <v>393</v>
       </c>
       <c r="J82" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -4199,7 +4196,7 @@
         <v>385</v>
       </c>
       <c r="J90" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -4315,7 +4312,7 @@
         <v>387</v>
       </c>
       <c r="J94" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4431,7 +4428,7 @@
         <v>400</v>
       </c>
       <c r="J98" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4460,7 +4457,7 @@
         <v>385</v>
       </c>
       <c r="J99" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4547,7 +4544,7 @@
         <v>385</v>
       </c>
       <c r="J102" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -4605,7 +4602,7 @@
         <v>384</v>
       </c>
       <c r="J104" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -4866,7 +4863,7 @@
         <v>393</v>
       </c>
       <c r="J113" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4924,7 +4921,7 @@
         <v>393</v>
       </c>
       <c r="J115" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -4953,7 +4950,7 @@
         <v>387</v>
       </c>
       <c r="J116" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:10">
